--- a/public/templates/question-import-template.xlsx
+++ b/public/templates/question-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Soal" sheetId="1" r:id="R0004293953504ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="Re4b8eb3549f9444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Soal" sheetId="1" r:id="R38f74768a9e44a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R0cc481d6a601412a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,7 +35,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0F766E"/>
+        <x:fgColor rgb="FF0B5DB4"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -46,48 +46,82 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QuestionImportExamples" displayName="QuestionImportExamples" ref="A1:W5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="23">
+    <x:tableColumn id="1" name="nama_tryout"/>
+    <x:tableColumn id="2" name="kode_soal"/>
+    <x:tableColumn id="3" name="jenis_soal"/>
+    <x:tableColumn id="4" name="sistem_penilaian"/>
+    <x:tableColumn id="5" name="bobot"/>
+    <x:tableColumn id="6" name="topik"/>
+    <x:tableColumn id="7" name="kode_topik"/>
+    <x:tableColumn id="8" name="kode_kisi_kisi"/>
+    <x:tableColumn id="9" name="tingkat_kesulitan"/>
+    <x:tableColumn id="10" name="status"/>
+    <x:tableColumn id="11" name="urutan_stimulus"/>
+    <x:tableColumn id="12" name="urutan_soal"/>
+    <x:tableColumn id="13" name="stimulus_html"/>
+    <x:tableColumn id="14" name="pertanyaan_html"/>
+    <x:tableColumn id="15" name="opsi_a"/>
+    <x:tableColumn id="16" name="opsi_b"/>
+    <x:tableColumn id="17" name="opsi_c"/>
+    <x:tableColumn id="18" name="opsi_d"/>
+    <x:tableColumn id="19" name="opsi_e"/>
+    <x:tableColumn id="20" name="matching_left"/>
+    <x:tableColumn id="21" name="matching_right"/>
+    <x:tableColumn id="22" name="kunci_jawaban"/>
+    <x:tableColumn id="23" name="pembahasan_html"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -133,9 +167,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -148,12 +182,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -244,266 +324,368 @@
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="32" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="22" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="22" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="38" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="45" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="20" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="10" t="str">
         <x:v>nama_tryout</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>kode_soal</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>jenis_soal</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>sistem_penilaian</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>bobot</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>topik</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="10" t="str">
+        <x:v>kode_topik</x:v>
+      </x:c>
+      <x:c r="H1" s="10" t="str">
         <x:v>kode_kisi_kisi</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>tingkat_kesulitan</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="10" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="K1" s="10" t="str">
         <x:v>urutan_stimulus</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="L1" s="10" t="str">
+        <x:v>urutan_soal</x:v>
+      </x:c>
+      <x:c r="M1" s="10" t="str">
         <x:v>stimulus_html</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="N1" s="10" t="str">
         <x:v>pertanyaan_html</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
+      <x:c r="O1" s="10" t="str">
         <x:v>opsi_a</x:v>
       </x:c>
-      <x:c r="N1" s="6" t="str">
+      <x:c r="P1" s="10" t="str">
         <x:v>opsi_b</x:v>
       </x:c>
-      <x:c r="O1" s="6" t="str">
+      <x:c r="Q1" s="10" t="str">
         <x:v>opsi_c</x:v>
       </x:c>
-      <x:c r="P1" s="6" t="str">
+      <x:c r="R1" s="10" t="str">
         <x:v>opsi_d</x:v>
       </x:c>
-      <x:c r="Q1" s="6" t="str">
+      <x:c r="S1" s="10" t="str">
         <x:v>opsi_e</x:v>
       </x:c>
-      <x:c r="R1" s="6" t="str">
+      <x:c r="T1" s="10" t="str">
+        <x:v>matching_left</x:v>
+      </x:c>
+      <x:c r="U1" s="10" t="str">
+        <x:v>matching_right</x:v>
+      </x:c>
+      <x:c r="V1" s="10" t="str">
         <x:v>kunci_jawaban</x:v>
       </x:c>
-      <x:c r="S1" s="6" t="str">
+      <x:c r="W1" s="10" t="str">
         <x:v>pembahasan_html</x:v>
       </x:c>
-      <x:c r="T1" s="6" t="str">
-        <x:v>catatan_format</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="12" t="str">
-        <x:v>Tryout Demo IPA SMP</x:v>
-      </x:c>
-      <x:c r="B2" s="12" t="str">
-        <x:v>Q-TKA-PG-001</x:v>
-      </x:c>
-      <x:c r="C2" s="12" t="str">
+    </x:row>
+    <x:row r="2" ht="72" customHeight="1">
+      <x:c r="A2" s="14" t="str">
+        <x:v>Contoh Ulangan IPA</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>IPA-PG-001</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
         <x:v>SINGLE_CHOICE</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="14" t="str">
         <x:v>EXACT_MATCH</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="n">
+      <x:c r="E2" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="14" t="str">
         <x:v>Gaya dan Gerak</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
-        <x:v>IPA-SMP-GERAK-001</x:v>
-      </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="G2" s="14" t="str">
+        <x:v>IPA-GERAK</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>KISI-IPA-001</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
         <x:v>Mudah</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
-        <x:v>PUBLISHED</x:v>
-      </x:c>
-      <x:c r="J2" s="12" t="n">
+      <x:c r="J2" s="14" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str"/>
-      <x:c r="L2" s="12" t="str">
-        <x:v>&lt;p&gt;Sebuah sepeda bermassa 20 kg mengalami percepatan 2 m/s². Besar gaya yang bekerja pada sepeda adalah ...&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="L2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str"/>
+      <x:c r="N2" s="14" t="str">
+        <x:v>&lt;p&gt;Sebuah benda bermassa 2 kg mengalami percepatan 3 m/s². Besar gaya resultannya adalah ...&lt;/p&gt;&lt;p&gt;Gunakan rumus \(F = ma\).&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="O2" s="14" t="str">
+        <x:v>3 N</x:v>
+      </x:c>
+      <x:c r="P2" s="14" t="str">
+        <x:v>5 N</x:v>
+      </x:c>
+      <x:c r="Q2" s="14" t="str">
+        <x:v>6 N</x:v>
+      </x:c>
+      <x:c r="R2" s="14" t="str">
+        <x:v>8 N</x:v>
+      </x:c>
+      <x:c r="S2" s="14" t="str">
         <x:v>10 N</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
-        <x:v>20 N</x:v>
-      </x:c>
-      <x:c r="O2" s="12" t="str">
-        <x:v>40 N</x:v>
-      </x:c>
-      <x:c r="P2" s="12" t="str">
-        <x:v>80 N</x:v>
-      </x:c>
-      <x:c r="Q2" s="12" t="str"/>
-      <x:c r="R2" s="12" t="str">
+      <x:c r="T2" s="14" t="str"/>
+      <x:c r="U2" s="14" t="str"/>
+      <x:c r="V2" s="14" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="S2" s="12" t="str">
-        <x:v>&lt;p&gt;F = m × a = 20 × 2 = 40 N.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="T2" s="12" t="str">
-        <x:v>PG biasa: isi satu kunci huruf, misalnya C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="12" t="str">
-        <x:v>Tryout Demo IPA SMP</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="str">
-        <x:v>Q-TKA-KOM-001</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="W2" s="14" t="str">
+        <x:v>&lt;p&gt;\(F = m a = 2 \times 3 = 6\text{ N}\), sehingga jawaban yang benar adalah C.&lt;/p&gt;</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="72" customHeight="1">
+      <x:c r="A3" s="14" t="str">
+        <x:v>Contoh Ulangan IPA</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>IPA-PGK-002</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
         <x:v>MULTIPLE_CHOICE</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="n">
+      <x:c r="E3" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>Sistem Pernapasan</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>IPA-BIO</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>KISI-IPA-002</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>Sedang</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
-        <x:v>Kalor dan Perubahan Wujud</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="str"/>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="L3" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M3" s="14" t="str"/>
+      <x:c r="N3" s="14" t="str">
+        <x:v>&lt;p&gt;Pilih &lt;strong&gt;semua&lt;/strong&gt; organ yang termasuk sistem pernapasan manusia.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="O3" s="14" t="str">
+        <x:v>Hidung</x:v>
+      </x:c>
+      <x:c r="P3" s="14" t="str">
+        <x:v>Trakea</x:v>
+      </x:c>
+      <x:c r="Q3" s="14" t="str">
+        <x:v>Paru-paru</x:v>
+      </x:c>
+      <x:c r="R3" s="14" t="str">
+        <x:v>Lambung</x:v>
+      </x:c>
+      <x:c r="S3" s="14" t="str">
+        <x:v>Ginjal</x:v>
+      </x:c>
+      <x:c r="T3" s="14" t="str"/>
+      <x:c r="U3" s="14" t="str"/>
+      <x:c r="V3" s="14" t="str">
+        <x:v>A,B,C</x:v>
+      </x:c>
+      <x:c r="W3" s="14" t="str">
+        <x:v>&lt;p&gt;Hidung, trakea, dan paru-paru merupakan bagian dari sistem pernapasan.&lt;/p&gt;</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="72" customHeight="1">
+      <x:c r="A4" s="14" t="str">
+        <x:v>Contoh Ulangan IPA</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>IPA-BS-003</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>TRUE_FALSE</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>PARTIAL_NO_PENALTY</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>Zat dan Perubahannya</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>IPA-KIMIA</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>KISI-IPA-003</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
         <x:v>Sedang</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
-        <x:v>PUBLISHED</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="n">
+      <x:c r="J4" s="14" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str"/>
-      <x:c r="L3" s="12" t="str">
-        <x:v>&lt;p&gt;Pilih semua pernyataan yang benar tentang energi pada benda yang jatuh.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="M3" s="12" t="str">
-        <x:v>Energi potensial bergantung pada massa, gravitasi, dan ketinggian.</x:v>
-      </x:c>
-      <x:c r="N3" s="12" t="str">
-        <x:v>Energi kinetik selalu nol selama benda bergerak jatuh.</x:v>
-      </x:c>
-      <x:c r="O3" s="12" t="str">
-        <x:v>Energi kinetik bertambah saat kecepatan benda meningkat.</x:v>
-      </x:c>
-      <x:c r="P3" s="12" t="str">
-        <x:v>Energi mekanik tetap jika hambatan udara diabaikan.</x:v>
-      </x:c>
-      <x:c r="Q3" s="12" t="str"/>
-      <x:c r="R3" s="12" t="str">
-        <x:v>A,C,D</x:v>
-      </x:c>
-      <x:c r="S3" s="12" t="str">
-        <x:v>&lt;p&gt;Kunci benar A, C, dan D. Pernyataan B salah karena benda yang bergerak memiliki energi kinetik.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="T3" s="12" t="str">
-        <x:v>PG kompleks: isi beberapa huruf dipisah koma, misalnya A,C,D</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="12" t="str">
-        <x:v>Tryout Demo IPA SMP</x:v>
-      </x:c>
-      <x:c r="B4" s="12" t="str">
-        <x:v>Q-TKA-BS-001</x:v>
-      </x:c>
-      <x:c r="C4" s="12" t="str">
-        <x:v>TRUE_FALSE</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="str">
+      <x:c r="L4" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str"/>
+      <x:c r="N4" s="14" t="str">
+        <x:v>&lt;p&gt;Tentukan apakah setiap pernyataan berikut &lt;strong&gt;Benar (B)&lt;/strong&gt; atau &lt;strong&gt;Salah (S)&lt;/strong&gt;.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="O4" s="14" t="str">
+        <x:v>Air membeku pada 0°C pada tekanan normal.</x:v>
+      </x:c>
+      <x:c r="P4" s="14" t="str">
+        <x:v>Penguapan hanya dapat terjadi pada suhu 100°C.</x:v>
+      </x:c>
+      <x:c r="Q4" s="14" t="str">
+        <x:v>Mencair adalah perubahan wujud padat menjadi cair.</x:v>
+      </x:c>
+      <x:c r="R4" s="14" t="str">
+        <x:v>Kondensasi adalah perubahan gas menjadi cair.</x:v>
+      </x:c>
+      <x:c r="S4" s="14" t="str"/>
+      <x:c r="T4" s="14" t="str"/>
+      <x:c r="U4" s="14" t="str"/>
+      <x:c r="V4" s="14" t="str">
+        <x:v>B,S,B,B</x:v>
+      </x:c>
+      <x:c r="W4" s="14" t="str">
+        <x:v>&lt;p&gt;Penguapan dapat terjadi pada berbagai suhu, sedangkan tiga pernyataan lainnya benar.&lt;/p&gt;</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="72" customHeight="1">
+      <x:c r="A5" s="14" t="str">
+        <x:v>Contoh Ulangan IPA</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>IPA-MATCH-004</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>MATCHING</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="n">
+      <x:c r="E5" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>Hukum Newton</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>IPA-FISIKA</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str">
+        <x:v>KISI-IPA-004</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>Sulit</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
-        <x:v>Ekosistem</x:v>
-      </x:c>
-      <x:c r="G4" s="12" t="str"/>
-      <x:c r="H4" s="12" t="str">
-        <x:v>Sedang</x:v>
-      </x:c>
-      <x:c r="I4" s="12" t="str">
-        <x:v>PUBLISHED</x:v>
-      </x:c>
-      <x:c r="J4" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K4" s="12" t="str"/>
-      <x:c r="L4" s="12" t="str">
-        <x:v>&lt;p&gt;Tentukan benar atau salah untuk setiap pernyataan tentang susunan atom oksigen.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="M4" s="12" t="str">
-        <x:v>Atom oksigen netral memiliki 8 elektron.</x:v>
-      </x:c>
-      <x:c r="N4" s="12" t="str">
-        <x:v>Jika nomor massanya 16, atom oksigen memiliki 7 neutron.</x:v>
-      </x:c>
-      <x:c r="O4" s="12" t="str">
-        <x:v>Kulit L pada atom oksigen berisi 6 elektron.</x:v>
-      </x:c>
-      <x:c r="P4" s="12" t="str"/>
-      <x:c r="Q4" s="12" t="str"/>
-      <x:c r="R4" s="12" t="str">
-        <x:v>B,S,B</x:v>
-      </x:c>
-      <x:c r="S4" s="12" t="str">
-        <x:v>&lt;p&gt;Oksigen netral memiliki 8 elektron. Nomor massa 16 berarti neutron 8. Kulit L berisi 6 elektron.&lt;/p&gt;</x:v>
-      </x:c>
-      <x:c r="T4" s="12" t="str">
-        <x:v>Benar salah: opsi_a sampai opsi_e diisi pernyataan. Kunci ditulis B,S,B sesuai urutan pernyataan.</x:v>
+      <x:c r="L5" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M5" s="14" t="str"/>
+      <x:c r="N5" s="14" t="str">
+        <x:v>&lt;p&gt;Jodohkan hukum Newton di kolom kiri dengan deskripsi/rumus yang tepat di kolom kanan.&lt;/p&gt;</x:v>
+      </x:c>
+      <x:c r="O5" s="14" t="str"/>
+      <x:c r="P5" s="14" t="str"/>
+      <x:c r="Q5" s="14" t="str"/>
+      <x:c r="R5" s="14" t="str"/>
+      <x:c r="S5" s="14" t="str"/>
+      <x:c r="T5" s="14" t="str">
+        <x:v>Hukum I Newton|Hukum II Newton|Hukum III Newton</x:v>
+      </x:c>
+      <x:c r="U5" s="14" t="str">
+        <x:v>F = ma|Aksi dan reaksi sama besar berlawanan arah|Benda mempertahankan keadaan geraknya</x:v>
+      </x:c>
+      <x:c r="V5" s="14" t="str">
+        <x:v>1:3|2:1|3:2</x:v>
+      </x:c>
+      <x:c r="W5" s="14" t="str">
+        <x:v>&lt;p&gt;Hukum I → inersia; Hukum II → \(F=ma\); Hukum III → aksi-reaksi.&lt;/p&gt;</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="C2:C200">
-      <x:formula1>"SINGLE_CHOICE,MULTIPLE_CHOICE,TRUE_FALSE"</x:formula1>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="C2:C500">
+      <x:formula1>"SINGLE_CHOICE,MULTIPLE_CHOICE,TRUE_FALSE,MATCHING"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="D2:D200">
+    <x:dataValidation type="list" sqref="D2:D500">
       <x:formula1>"EXACT_MATCH,PARTIAL_NO_PENALTY"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="I2:I200">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"Mudah,Sedang,Sulit"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J500">
       <x:formula1>"DRAFT,REVIEW,PUBLISHED,ARCHIVED"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ea30c2e51204d6d"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -511,121 +693,103 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="90" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Kolom</x:v>
-      </x:c>
-      <x:c r="B1" s="5" t="str">
-        <x:v>Keterangan</x:v>
-      </x:c>
+      <x:c r="A1" s="16" t="str">
+        <x:v>TEMPLATE IMPORT SOAL SAINSMASAMBA</x:v>
+      </x:c>
+      <x:c r="B1" s="16" t="str"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>jenis_soal</x:v>
+        <x:v>Jenis soal yang didukung</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
-        <x:v>SINGLE_CHOICE untuk pilihan ganda biasa, MULTIPLE_CHOICE untuk pilihan ganda kompleks, TRUE_FALSE untuk benar atau salah.</x:v>
+        <x:v>SINGLE_CHOICE, MULTIPLE_CHOICE, TRUE_FALSE, MATCHING</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>sistem_penilaian</x:v>
+        <x:v>SINGLE_CHOICE</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>EXACT_MATCH memberi skor penuh hanya jika jawaban sama persis. PARTIAL_NO_PENALTY memberi skor parsial tanpa pengurangan untuk pilihan salah.</x:v>
+        <x:v>Isi opsi_a s.d. opsi_e seperlunya. kunci_jawaban satu huruf, contoh: C.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>kunci_jawaban untuk SINGLE_CHOICE</x:v>
+        <x:v>MULTIPLE_CHOICE</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>Isi satu huruf, contoh C.</x:v>
+        <x:v>Isi opsi. kunci_jawaban beberapa huruf dipisah koma, contoh: A,B,C.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>kunci_jawaban untuk MULTIPLE_CHOICE</x:v>
+        <x:v>TRUE_FALSE</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Isi beberapa huruf dipisah koma, contoh A,C,D.</x:v>
+        <x:v>Gunakan opsi_a, opsi_b, dst. sebagai pernyataan. kunci_jawaban contoh: B,S,B,B.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>kunci_jawaban untuk TRUE_FALSE</x:v>
+        <x:v>MATCHING</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>Isi B atau S sesuai urutan pernyataan pada opsi_a sampai opsi_e. Contoh B,S,B berarti pernyataan 1 benar, 2 salah, 3 benar.</x:v>
+        <x:v>Isi matching_left dan matching_right dengan pemisah |. kunci_jawaban contoh: 1:3|2:1|3:2.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>bobot</x:v>
+        <x:v>matching_left</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Nilai maksimal per soal. Umumnya 1.</x:v>
+        <x:v>Contoh: Hukum I Newton|Hukum II Newton|Hukum III Newton</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>HTML dan LaTeX</x:v>
+        <x:v>matching_right</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Kolom stimulus_html, pertanyaan_html, opsi, dan pembahasan_html dapat diisi HTML sederhana atau rumus LaTeX.</x:v>
+        <x:v>Contoh: F = ma|Aksi dan reaksi...|Benda mempertahankan keadaan geraknya</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12"/>
-      <x:c r="B9" s="12"/>
+      <x:c r="A9" s="12" t="str">
+        <x:v>Kunci MATCHING</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>1:3 berarti item kiri nomor 1 dipasangkan dengan item kanan nomor 3.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12"/>
-      <x:c r="B10" s="12"/>
+      <x:c r="A10" s="12" t="str">
+        <x:v>WYSIWYG / HTML</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>Kolom stimulus_html, pertanyaan_html, dan pembahasan_html boleh berisi HTML sederhana.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12"/>
-      <x:c r="B11" s="12"/>
+      <x:c r="A11" s="12" t="str">
+        <x:v>LaTeX</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>Gunakan \( ... \) untuk inline atau \[ ... \] untuk display, contoh: \(F=ma\).</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="12"/>
-      <x:c r="B12" s="12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="12"/>
-      <x:c r="B13" s="12"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="12"/>
-      <x:c r="B14" s="12"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="12"/>
-      <x:c r="B17" s="12"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="12"/>
-      <x:c r="B18" s="12"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="12"/>
-      <x:c r="B19" s="12"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="12"/>
-      <x:c r="B20" s="12"/>
+      <x:c r="A12" s="12" t="str">
+        <x:v>Kompatibilitas</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>Tiga tipe lama tetap memakai format sebelumnya; kolom matching_left dan matching_right boleh kosong.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/templates/question-import-template.xlsx
+++ b/public/templates/question-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Soal" sheetId="1" r:id="R38f74768a9e44a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R0cc481d6a601412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Soal" sheetId="1" r:id="Rc504eb57fe144cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="Rfa712eeb6ec8492f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,27 +46,27 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,51 +77,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QuestionImportExamples" displayName="QuestionImportExamples" ref="A1:W5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="23">
-    <x:tableColumn id="1" name="nama_tryout"/>
-    <x:tableColumn id="2" name="kode_soal"/>
-    <x:tableColumn id="3" name="jenis_soal"/>
-    <x:tableColumn id="4" name="sistem_penilaian"/>
-    <x:tableColumn id="5" name="bobot"/>
-    <x:tableColumn id="6" name="topik"/>
-    <x:tableColumn id="7" name="kode_topik"/>
-    <x:tableColumn id="8" name="kode_kisi_kisi"/>
-    <x:tableColumn id="9" name="tingkat_kesulitan"/>
-    <x:tableColumn id="10" name="status"/>
-    <x:tableColumn id="11" name="urutan_stimulus"/>
-    <x:tableColumn id="12" name="urutan_soal"/>
-    <x:tableColumn id="13" name="stimulus_html"/>
-    <x:tableColumn id="14" name="pertanyaan_html"/>
-    <x:tableColumn id="15" name="opsi_a"/>
-    <x:tableColumn id="16" name="opsi_b"/>
-    <x:tableColumn id="17" name="opsi_c"/>
-    <x:tableColumn id="18" name="opsi_d"/>
-    <x:tableColumn id="19" name="opsi_e"/>
-    <x:tableColumn id="20" name="matching_left"/>
-    <x:tableColumn id="21" name="matching_right"/>
-    <x:tableColumn id="22" name="kunci_jawaban"/>
-    <x:tableColumn id="23" name="pembahasan_html"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -319,373 +279,372 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="38" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="22" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="22" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="38" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="45" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="20" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="22" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="36" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="40" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="10" t="str">
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>nama_tryout</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="6" t="str">
+        <x:v>kategori_soal</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
         <x:v>kode_soal</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>jenis_soal</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>sistem_penilaian</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>bobot</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>topik</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>kode_topik</x:v>
       </x:c>
-      <x:c r="H1" s="10" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>kode_kisi_kisi</x:v>
       </x:c>
-      <x:c r="I1" s="10" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>tingkat_kesulitan</x:v>
       </x:c>
-      <x:c r="J1" s="10" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="K1" s="10" t="str">
+      <x:c r="L1" s="6" t="str">
         <x:v>urutan_stimulus</x:v>
       </x:c>
-      <x:c r="L1" s="10" t="str">
+      <x:c r="M1" s="6" t="str">
         <x:v>urutan_soal</x:v>
       </x:c>
-      <x:c r="M1" s="10" t="str">
+      <x:c r="N1" s="6" t="str">
         <x:v>stimulus_html</x:v>
       </x:c>
-      <x:c r="N1" s="10" t="str">
+      <x:c r="O1" s="6" t="str">
         <x:v>pertanyaan_html</x:v>
       </x:c>
-      <x:c r="O1" s="10" t="str">
+      <x:c r="P1" s="6" t="str">
         <x:v>opsi_a</x:v>
       </x:c>
-      <x:c r="P1" s="10" t="str">
+      <x:c r="Q1" s="6" t="str">
         <x:v>opsi_b</x:v>
       </x:c>
-      <x:c r="Q1" s="10" t="str">
+      <x:c r="R1" s="6" t="str">
         <x:v>opsi_c</x:v>
       </x:c>
-      <x:c r="R1" s="10" t="str">
+      <x:c r="S1" s="6" t="str">
         <x:v>opsi_d</x:v>
       </x:c>
-      <x:c r="S1" s="10" t="str">
+      <x:c r="T1" s="6" t="str">
         <x:v>opsi_e</x:v>
       </x:c>
-      <x:c r="T1" s="10" t="str">
+      <x:c r="U1" s="6" t="str">
         <x:v>matching_left</x:v>
       </x:c>
-      <x:c r="U1" s="10" t="str">
+      <x:c r="V1" s="6" t="str">
         <x:v>matching_right</x:v>
       </x:c>
-      <x:c r="V1" s="10" t="str">
+      <x:c r="W1" s="6" t="str">
         <x:v>kunci_jawaban</x:v>
       </x:c>
-      <x:c r="W1" s="10" t="str">
+      <x:c r="X1" s="6" t="str">
         <x:v>pembahasan_html</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="72" customHeight="1">
-      <x:c r="A2" s="14" t="str">
+    <x:row r="2" ht="36" customHeight="1">
+      <x:c r="A2" s="12" t="str">
         <x:v>Contoh Ulangan IPA</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
+      <x:c r="B2" s="12" t="str">
+        <x:v>Ulangan Harian</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
         <x:v>IPA-PG-001</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>SINGLE_CHOICE</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
+      <x:c r="E2" s="12" t="str">
         <x:v>EXACT_MATCH</x:v>
       </x:c>
-      <x:c r="E2" s="14" t="n">
+      <x:c r="F2" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="14" t="str">
+      <x:c r="G2" s="12" t="str">
         <x:v>Gaya dan Gerak</x:v>
       </x:c>
-      <x:c r="G2" s="14" t="str">
+      <x:c r="H2" s="12" t="str">
         <x:v>IPA-GERAK</x:v>
       </x:c>
-      <x:c r="H2" s="14" t="str">
+      <x:c r="I2" s="12" t="str">
         <x:v>KISI-IPA-001</x:v>
       </x:c>
-      <x:c r="I2" s="14" t="str">
+      <x:c r="J2" s="12" t="str">
         <x:v>Mudah</x:v>
       </x:c>
-      <x:c r="J2" s="14" t="str">
+      <x:c r="K2" s="12" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
-      <x:c r="K2" s="14" t="n">
+      <x:c r="L2" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L2" s="14" t="n">
+      <x:c r="M2" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M2" s="14" t="str"/>
-      <x:c r="N2" s="14" t="str">
+      <x:c r="N2" s="12" t="str"/>
+      <x:c r="O2" s="12" t="str">
         <x:v>&lt;p&gt;Sebuah benda bermassa 2 kg mengalami percepatan 3 m/s². Besar gaya resultannya adalah ...&lt;/p&gt;&lt;p&gt;Gunakan rumus \(F = ma\).&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="O2" s="14" t="str">
+      <x:c r="P2" s="12" t="str">
         <x:v>3 N</x:v>
       </x:c>
-      <x:c r="P2" s="14" t="str">
+      <x:c r="Q2" s="12" t="str">
         <x:v>5 N</x:v>
       </x:c>
-      <x:c r="Q2" s="14" t="str">
+      <x:c r="R2" s="12" t="str">
         <x:v>6 N</x:v>
       </x:c>
-      <x:c r="R2" s="14" t="str">
+      <x:c r="S2" s="12" t="str">
         <x:v>8 N</x:v>
       </x:c>
-      <x:c r="S2" s="14" t="str">
+      <x:c r="T2" s="12" t="str">
         <x:v>10 N</x:v>
       </x:c>
-      <x:c r="T2" s="14" t="str"/>
-      <x:c r="U2" s="14" t="str"/>
-      <x:c r="V2" s="14" t="str">
+      <x:c r="U2" s="12" t="str"/>
+      <x:c r="V2" s="12" t="str"/>
+      <x:c r="W2" s="12" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="W2" s="14" t="str">
+      <x:c r="X2" s="12" t="str">
         <x:v>&lt;p&gt;\(F = m a = 2 \times 3 = 6\text{ N}\), sehingga jawaban yang benar adalah C.&lt;/p&gt;</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="72" customHeight="1">
-      <x:c r="A3" s="14" t="str">
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="12" t="str">
         <x:v>Contoh Ulangan IPA</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="12" t="str">
+        <x:v>Ulangan Harian</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="str">
         <x:v>IPA-PGK-002</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="D3" s="12" t="str">
         <x:v>MULTIPLE_CHOICE</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="E3" s="12" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="n">
+      <x:c r="F3" s="12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="str">
+      <x:c r="G3" s="12" t="str">
         <x:v>Sistem Pernapasan</x:v>
       </x:c>
-      <x:c r="G3" s="14" t="str">
+      <x:c r="H3" s="12" t="str">
         <x:v>IPA-BIO</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="str">
+      <x:c r="I3" s="12" t="str">
         <x:v>KISI-IPA-002</x:v>
       </x:c>
-      <x:c r="I3" s="14" t="str">
+      <x:c r="J3" s="12" t="str">
         <x:v>Sedang</x:v>
       </x:c>
-      <x:c r="J3" s="14" t="str">
+      <x:c r="K3" s="12" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
-      <x:c r="K3" s="14" t="n">
+      <x:c r="L3" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L3" s="14" t="n">
+      <x:c r="M3" s="12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M3" s="14" t="str"/>
-      <x:c r="N3" s="14" t="str">
+      <x:c r="N3" s="12" t="str"/>
+      <x:c r="O3" s="12" t="str">
         <x:v>&lt;p&gt;Pilih &lt;strong&gt;semua&lt;/strong&gt; organ yang termasuk sistem pernapasan manusia.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="O3" s="14" t="str">
+      <x:c r="P3" s="12" t="str">
         <x:v>Hidung</x:v>
       </x:c>
-      <x:c r="P3" s="14" t="str">
+      <x:c r="Q3" s="12" t="str">
         <x:v>Trakea</x:v>
       </x:c>
-      <x:c r="Q3" s="14" t="str">
+      <x:c r="R3" s="12" t="str">
         <x:v>Paru-paru</x:v>
       </x:c>
-      <x:c r="R3" s="14" t="str">
+      <x:c r="S3" s="12" t="str">
         <x:v>Lambung</x:v>
       </x:c>
-      <x:c r="S3" s="14" t="str">
+      <x:c r="T3" s="12" t="str">
         <x:v>Ginjal</x:v>
       </x:c>
-      <x:c r="T3" s="14" t="str"/>
-      <x:c r="U3" s="14" t="str"/>
-      <x:c r="V3" s="14" t="str">
+      <x:c r="U3" s="12" t="str"/>
+      <x:c r="V3" s="12" t="str"/>
+      <x:c r="W3" s="12" t="str">
         <x:v>A,B,C</x:v>
       </x:c>
-      <x:c r="W3" s="14" t="str">
+      <x:c r="X3" s="12" t="str">
         <x:v>&lt;p&gt;Hidung, trakea, dan paru-paru merupakan bagian dari sistem pernapasan.&lt;/p&gt;</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="72" customHeight="1">
-      <x:c r="A4" s="14" t="str">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="12" t="str">
         <x:v>Contoh Ulangan IPA</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
+      <x:c r="B4" s="12" t="str">
+        <x:v>Ulangan Harian</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
         <x:v>IPA-BS-003</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
+      <x:c r="D4" s="12" t="str">
         <x:v>TRUE_FALSE</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
+      <x:c r="E4" s="12" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="n">
+      <x:c r="F4" s="12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="14" t="str">
+      <x:c r="G4" s="12" t="str">
         <x:v>Zat dan Perubahannya</x:v>
       </x:c>
-      <x:c r="G4" s="14" t="str">
+      <x:c r="H4" s="12" t="str">
         <x:v>IPA-KIMIA</x:v>
       </x:c>
-      <x:c r="H4" s="14" t="str">
+      <x:c r="I4" s="12" t="str">
         <x:v>KISI-IPA-003</x:v>
       </x:c>
-      <x:c r="I4" s="14" t="str">
+      <x:c r="J4" s="12" t="str">
         <x:v>Sedang</x:v>
       </x:c>
-      <x:c r="J4" s="14" t="str">
+      <x:c r="K4" s="12" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
-      <x:c r="K4" s="14" t="n">
+      <x:c r="L4" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L4" s="14" t="n">
+      <x:c r="M4" s="12" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M4" s="14" t="str"/>
-      <x:c r="N4" s="14" t="str">
+      <x:c r="N4" s="12" t="str"/>
+      <x:c r="O4" s="12" t="str">
         <x:v>&lt;p&gt;Tentukan apakah setiap pernyataan berikut &lt;strong&gt;Benar (B)&lt;/strong&gt; atau &lt;strong&gt;Salah (S)&lt;/strong&gt;.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="O4" s="14" t="str">
+      <x:c r="P4" s="12" t="str">
         <x:v>Air membeku pada 0°C pada tekanan normal.</x:v>
       </x:c>
-      <x:c r="P4" s="14" t="str">
+      <x:c r="Q4" s="12" t="str">
         <x:v>Penguapan hanya dapat terjadi pada suhu 100°C.</x:v>
       </x:c>
-      <x:c r="Q4" s="14" t="str">
+      <x:c r="R4" s="12" t="str">
         <x:v>Mencair adalah perubahan wujud padat menjadi cair.</x:v>
       </x:c>
-      <x:c r="R4" s="14" t="str">
+      <x:c r="S4" s="12" t="str">
         <x:v>Kondensasi adalah perubahan gas menjadi cair.</x:v>
       </x:c>
-      <x:c r="S4" s="14" t="str"/>
-      <x:c r="T4" s="14" t="str"/>
-      <x:c r="U4" s="14" t="str"/>
-      <x:c r="V4" s="14" t="str">
+      <x:c r="T4" s="12" t="str"/>
+      <x:c r="U4" s="12" t="str"/>
+      <x:c r="V4" s="12" t="str"/>
+      <x:c r="W4" s="12" t="str">
         <x:v>B,S,B,B</x:v>
       </x:c>
-      <x:c r="W4" s="14" t="str">
+      <x:c r="X4" s="12" t="str">
         <x:v>&lt;p&gt;Penguapan dapat terjadi pada berbagai suhu, sedangkan tiga pernyataan lainnya benar.&lt;/p&gt;</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="72" customHeight="1">
-      <x:c r="A5" s="14" t="str">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="12" t="str">
         <x:v>Contoh Ulangan IPA</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="str">
+      <x:c r="B5" s="12" t="str">
+        <x:v>Ulangan Harian</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
         <x:v>IPA-MATCH-004</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
+      <x:c r="D5" s="12" t="str">
         <x:v>MATCHING</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str">
+      <x:c r="E5" s="12" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="n">
+      <x:c r="F5" s="12" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F5" s="14" t="str">
+      <x:c r="G5" s="12" t="str">
         <x:v>Hukum Newton</x:v>
       </x:c>
-      <x:c r="G5" s="14" t="str">
+      <x:c r="H5" s="12" t="str">
         <x:v>IPA-FISIKA</x:v>
       </x:c>
-      <x:c r="H5" s="14" t="str">
+      <x:c r="I5" s="12" t="str">
         <x:v>KISI-IPA-004</x:v>
       </x:c>
-      <x:c r="I5" s="14" t="str">
+      <x:c r="J5" s="12" t="str">
         <x:v>Sulit</x:v>
       </x:c>
-      <x:c r="J5" s="14" t="str">
+      <x:c r="K5" s="12" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
-      <x:c r="K5" s="14" t="n">
+      <x:c r="L5" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L5" s="14" t="n">
+      <x:c r="M5" s="12" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M5" s="14" t="str"/>
-      <x:c r="N5" s="14" t="str">
+      <x:c r="N5" s="12" t="str"/>
+      <x:c r="O5" s="12" t="str">
         <x:v>&lt;p&gt;Jodohkan hukum Newton di kolom kiri dengan deskripsi/rumus yang tepat di kolom kanan.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="O5" s="14" t="str"/>
-      <x:c r="P5" s="14" t="str"/>
-      <x:c r="Q5" s="14" t="str"/>
-      <x:c r="R5" s="14" t="str"/>
-      <x:c r="S5" s="14" t="str"/>
-      <x:c r="T5" s="14" t="str">
+      <x:c r="P5" s="12" t="str"/>
+      <x:c r="Q5" s="12" t="str"/>
+      <x:c r="R5" s="12" t="str"/>
+      <x:c r="S5" s="12" t="str"/>
+      <x:c r="T5" s="12" t="str"/>
+      <x:c r="U5" s="12" t="str">
         <x:v>Hukum I Newton|Hukum II Newton|Hukum III Newton</x:v>
       </x:c>
-      <x:c r="U5" s="14" t="str">
+      <x:c r="V5" s="12" t="str">
         <x:v>F = ma|Aksi dan reaksi sama besar berlawanan arah|Benda mempertahankan keadaan geraknya</x:v>
       </x:c>
-      <x:c r="V5" s="14" t="str">
+      <x:c r="W5" s="12" t="str">
         <x:v>1:3|2:1|3:2</x:v>
       </x:c>
-      <x:c r="W5" s="14" t="str">
+      <x:c r="X5" s="12" t="str">
         <x:v>&lt;p&gt;Hukum I → inersia; Hukum II → \(F=ma\); Hukum III → aksi-reaksi.&lt;/p&gt;</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="C2:C500">
-      <x:formula1>"SINGLE_CHOICE,MULTIPLE_CHOICE,TRUE_FALSE,MATCHING"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="D2:D500">
-      <x:formula1>"EXACT_MATCH,PARTIAL_NO_PENALTY"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="I2:I500">
-      <x:formula1>"Mudah,Sedang,Sulit"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J2:J500">
-      <x:formula1>"DRAFT,REVIEW,PUBLISHED,ARCHIVED"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ea30c2e51204d6d"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -693,102 +652,86 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+      <x:c r="A1" s="4" t="str">
         <x:v>TEMPLATE IMPORT SOAL SAINSMASAMBA</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str"/>
+      <x:c r="B1" s="4" t="str"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>Jenis soal yang didukung</x:v>
+        <x:v>Kolom paket soal</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
-        <x:v>SINGLE_CHOICE, MULTIPLE_CHOICE, TRUE_FALSE, MATCHING</x:v>
+        <x:v>nama_tryout = nama paket soal; kategori_soal = kategori seperti Ulangan Harian, PTS, PAS, Tryout, Remedial.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>SINGLE_CHOICE</x:v>
+        <x:v>Saat membuat jadwal</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>Isi opsi_a s.d. opsi_e seperlunya. kunci_jawaban satu huruf, contoh: C.</x:v>
+        <x:v>Guru dapat memilih kategori lalu paket soal. Soal berstatus PUBLISHED/ACTIVE dari paket akan dipetakan otomatis ke ujian.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>MULTIPLE_CHOICE</x:v>
+        <x:v>Jenis soal yang didukung</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>Isi opsi. kunci_jawaban beberapa huruf dipisah koma, contoh: A,B,C.</x:v>
+        <x:v>SINGLE_CHOICE, MULTIPLE_CHOICE, TRUE_FALSE, MATCHING</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>TRUE_FALSE</x:v>
+        <x:v>SINGLE_CHOICE</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Gunakan opsi_a, opsi_b, dst. sebagai pernyataan. kunci_jawaban contoh: B,S,B,B.</x:v>
+        <x:v>Isi opsi_a s.d. opsi_e seperlunya. kunci_jawaban satu huruf, contoh: C.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>MATCHING</x:v>
+        <x:v>MULTIPLE_CHOICE</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>Isi matching_left dan matching_right dengan pemisah |. kunci_jawaban contoh: 1:3|2:1|3:2.</x:v>
+        <x:v>Isi opsi. kunci_jawaban beberapa huruf dipisah koma, contoh: A,B,C.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>matching_left</x:v>
+        <x:v>TRUE_FALSE</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Contoh: Hukum I Newton|Hukum II Newton|Hukum III Newton</x:v>
+        <x:v>Gunakan opsi_a, opsi_b, dst. sebagai pernyataan. kunci_jawaban contoh: B,S,B,B.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>matching_right</x:v>
+        <x:v>MATCHING</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Contoh: F = ma|Aksi dan reaksi...|Benda mempertahankan keadaan geraknya</x:v>
+        <x:v>Isi matching_left dan matching_right dengan pemisah |. kunci_jawaban contoh: 1:3|2:1|3:2.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>Kunci MATCHING</x:v>
+        <x:v>Status agar bisa dijadwalkan</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>1:3 berarti item kiri nomor 1 dipasangkan dengan item kanan nomor 3.</x:v>
+        <x:v>Gunakan PUBLISHED (atau ACTIVE) agar soal dapat otomatis dipakai saat paket dipilih pada jadwal.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
-        <x:v>WYSIWYG / HTML</x:v>
+        <x:v>Backward compatible</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Kolom stimulus_html, pertanyaan_html, dan pembahasan_html boleh berisi HTML sederhana.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="12" t="str">
-        <x:v>LaTeX</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="str">
-        <x:v>Gunakan \( ... \) untuk inline atau \[ ... \] untuk display, contoh: \(F=ma\).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="12" t="str">
-        <x:v>Kompatibilitas</x:v>
-      </x:c>
-      <x:c r="B12" s="12" t="str">
-        <x:v>Tiga tipe lama tetap memakai format sebelumnya; kolom matching_left dan matching_right boleh kosong.</x:v>
+        <x:v>File lama tanpa kategori_soal tetap dapat dibaca; aplikasi akan mencoba menginfer kategori dari nama_tryout.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
